--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122373350</v>
+        <v>122373381</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480089</v>
+        <v>480295</v>
       </c>
       <c r="R2" t="n">
-        <v>7056809</v>
+        <v>7056917</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122373382</v>
+        <v>122373373</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480323</v>
+        <v>480214</v>
       </c>
       <c r="R3" t="n">
-        <v>7056911</v>
+        <v>7056710</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122373381</v>
+        <v>122373363</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480295</v>
+        <v>479932</v>
       </c>
       <c r="R4" t="n">
-        <v>7056917</v>
+        <v>7056162</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122373373</v>
+        <v>122373368</v>
       </c>
       <c r="B5" t="n">
         <v>57374</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480214</v>
+        <v>479912</v>
       </c>
       <c r="R5" t="n">
-        <v>7056710</v>
+        <v>7056484</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122373374</v>
+        <v>122373351</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480232</v>
+        <v>480019</v>
       </c>
       <c r="R6" t="n">
-        <v>7056719</v>
+        <v>7056686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122373376</v>
+        <v>122373379</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1243,37 +1243,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480199</v>
+        <v>480196</v>
       </c>
       <c r="R7" t="n">
-        <v>7056785</v>
+        <v>7056852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122373375</v>
+        <v>122373361</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1372,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480254</v>
+        <v>479902</v>
       </c>
       <c r="R8" t="n">
-        <v>7056771</v>
+        <v>7056188</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122373353</v>
+        <v>122373382</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1479,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479911</v>
+        <v>480323</v>
       </c>
       <c r="R9" t="n">
-        <v>7056543</v>
+        <v>7056911</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122373384</v>
+        <v>122373377</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1586,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480354</v>
+        <v>480176</v>
       </c>
       <c r="R10" t="n">
-        <v>7056915</v>
+        <v>7056807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122373357</v>
+        <v>122373388</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1693,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479865</v>
+        <v>480408</v>
       </c>
       <c r="R11" t="n">
-        <v>7056258</v>
+        <v>7056973</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122373393</v>
+        <v>122373352</v>
       </c>
       <c r="B12" t="n">
-        <v>57527</v>
+        <v>57374</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,46 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480298</v>
+        <v>479988</v>
       </c>
       <c r="R12" t="n">
-        <v>7056795</v>
+        <v>7056637</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122373358</v>
+        <v>122373342</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1914,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479856</v>
+        <v>480287</v>
       </c>
       <c r="R13" t="n">
-        <v>7056220</v>
+        <v>7056982</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122373396</v>
+        <v>122373397</v>
       </c>
       <c r="B14" t="n">
-        <v>57485</v>
+        <v>78645</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,46 +1971,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480182</v>
+        <v>480312</v>
       </c>
       <c r="R14" t="n">
-        <v>7056798</v>
+        <v>7056795</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122373355</v>
+        <v>122373376</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2124,17 +2094,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479798</v>
+        <v>480199</v>
       </c>
       <c r="R15" t="n">
-        <v>7056352</v>
+        <v>7056785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,11 +2157,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122373367</v>
+        <v>122373353</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2241,7 +2226,7 @@
         <v>479911</v>
       </c>
       <c r="R16" t="n">
-        <v>7056478</v>
+        <v>7056543</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,7 +2263,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122373352</v>
+        <v>122373386</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2345,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479988</v>
+        <v>480360</v>
       </c>
       <c r="R17" t="n">
-        <v>7056637</v>
+        <v>7056924</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2385,7 +2370,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122373366</v>
+        <v>122373347</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2452,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479875</v>
+        <v>480230</v>
       </c>
       <c r="R18" t="n">
-        <v>7056356</v>
+        <v>7056904</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122373344</v>
+        <v>122373398</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480283</v>
+        <v>480268</v>
       </c>
       <c r="R19" t="n">
-        <v>7056981</v>
+        <v>7056775</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,11 +2580,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122373389</v>
+        <v>122373358</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2666,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480418</v>
+        <v>479856</v>
       </c>
       <c r="R20" t="n">
-        <v>7056980</v>
+        <v>7056220</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,7 +2713,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122373356</v>
+        <v>122373384</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2773,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479919</v>
+        <v>480354</v>
       </c>
       <c r="R21" t="n">
-        <v>7056272</v>
+        <v>7056915</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,7 +2820,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122373368</v>
+        <v>122373372</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2880,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479912</v>
+        <v>480193</v>
       </c>
       <c r="R22" t="n">
-        <v>7056484</v>
+        <v>7056693</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2947,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122373370</v>
+        <v>122373396</v>
       </c>
       <c r="B23" t="n">
-        <v>57374</v>
+        <v>57485</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2959,20 +2939,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2980,17 +2960,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480000</v>
+        <v>480182</v>
       </c>
       <c r="R23" t="n">
-        <v>7056521</v>
+        <v>7056798</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,11 +3011,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3054,10 +3037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122373378</v>
+        <v>122373392</v>
       </c>
       <c r="B24" t="n">
-        <v>57374</v>
+        <v>56584</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3066,38 +3049,54 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480182</v>
+        <v>480100</v>
       </c>
       <c r="R24" t="n">
-        <v>7056855</v>
+        <v>7056572</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,11 +3129,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,7 +3155,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122373349</v>
+        <v>122373369</v>
       </c>
       <c r="B25" t="n">
         <v>57374</v>
@@ -3201,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480109</v>
+        <v>479913</v>
       </c>
       <c r="R25" t="n">
-        <v>7056820</v>
+        <v>7056490</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,7 +3262,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122373363</v>
+        <v>122373354</v>
       </c>
       <c r="B26" t="n">
         <v>57374</v>
@@ -3308,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479932</v>
+        <v>479919</v>
       </c>
       <c r="R26" t="n">
-        <v>7056162</v>
+        <v>7056527</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3369,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122373385</v>
+        <v>122373370</v>
       </c>
       <c r="B27" t="n">
         <v>57374</v>
@@ -3415,10 +3409,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480361</v>
+        <v>480000</v>
       </c>
       <c r="R27" t="n">
-        <v>7056919</v>
+        <v>7056521</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3482,7 +3476,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122373351</v>
+        <v>122373350</v>
       </c>
       <c r="B28" t="n">
         <v>57374</v>
@@ -3522,10 +3516,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480019</v>
+        <v>480089</v>
       </c>
       <c r="R28" t="n">
-        <v>7056686</v>
+        <v>7056809</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,7 +3556,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,7 +3583,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122373348</v>
+        <v>122373385</v>
       </c>
       <c r="B29" t="n">
         <v>57374</v>
@@ -3629,10 +3623,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480205</v>
+        <v>480361</v>
       </c>
       <c r="R29" t="n">
-        <v>7056888</v>
+        <v>7056919</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,7 +3663,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3690,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122373397</v>
+        <v>122373344</v>
       </c>
       <c r="B30" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3712,21 +3706,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3736,10 +3730,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480312</v>
+        <v>480283</v>
       </c>
       <c r="R30" t="n">
-        <v>7056795</v>
+        <v>7056981</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3772,6 +3766,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3798,7 +3797,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122373362</v>
+        <v>122373374</v>
       </c>
       <c r="B31" t="n">
         <v>57374</v>
@@ -3838,10 +3837,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479917</v>
+        <v>480232</v>
       </c>
       <c r="R31" t="n">
-        <v>7056160</v>
+        <v>7056719</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3905,7 +3904,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122373354</v>
+        <v>122373356</v>
       </c>
       <c r="B32" t="n">
         <v>57374</v>
@@ -3948,7 +3947,7 @@
         <v>479919</v>
       </c>
       <c r="R32" t="n">
-        <v>7056527</v>
+        <v>7056272</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,7 +3984,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4012,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122373398</v>
+        <v>122373380</v>
       </c>
       <c r="B33" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4028,21 +4027,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4052,10 +4051,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480268</v>
+        <v>480203</v>
       </c>
       <c r="R33" t="n">
-        <v>7056775</v>
+        <v>7056860</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4088,6 +4087,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4114,7 +4118,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122373345</v>
+        <v>122373366</v>
       </c>
       <c r="B34" t="n">
         <v>57374</v>
@@ -4154,10 +4158,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480279</v>
+        <v>479875</v>
       </c>
       <c r="R34" t="n">
-        <v>7056943</v>
+        <v>7056356</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4194,7 +4198,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4221,10 +4225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122373386</v>
+        <v>122373393</v>
       </c>
       <c r="B35" t="n">
-        <v>57374</v>
+        <v>57527</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4237,34 +4241,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480360</v>
+        <v>480298</v>
       </c>
       <c r="R35" t="n">
-        <v>7056924</v>
+        <v>7056795</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,11 +4313,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4328,7 +4339,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122373388</v>
+        <v>122373383</v>
       </c>
       <c r="B36" t="n">
         <v>57374</v>
@@ -4368,10 +4379,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480408</v>
+        <v>480360</v>
       </c>
       <c r="R36" t="n">
-        <v>7056973</v>
+        <v>7056891</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4408,7 +4419,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4435,7 +4446,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122373347</v>
+        <v>122373359</v>
       </c>
       <c r="B37" t="n">
         <v>57374</v>
@@ -4475,10 +4486,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480230</v>
+        <v>479854</v>
       </c>
       <c r="R37" t="n">
-        <v>7056904</v>
+        <v>7056208</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4542,7 +4553,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122373361</v>
+        <v>122373389</v>
       </c>
       <c r="B38" t="n">
         <v>57374</v>
@@ -4582,10 +4593,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479902</v>
+        <v>480418</v>
       </c>
       <c r="R38" t="n">
-        <v>7056188</v>
+        <v>7056980</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4649,7 +4660,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122373383</v>
+        <v>122373378</v>
       </c>
       <c r="B39" t="n">
         <v>57374</v>
@@ -4689,10 +4700,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480360</v>
+        <v>480182</v>
       </c>
       <c r="R39" t="n">
-        <v>7056891</v>
+        <v>7056855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4756,7 +4767,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122373342</v>
+        <v>122373375</v>
       </c>
       <c r="B40" t="n">
         <v>57374</v>
@@ -4796,10 +4807,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480287</v>
+        <v>480254</v>
       </c>
       <c r="R40" t="n">
-        <v>7056982</v>
+        <v>7056771</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4836,7 +4847,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4863,7 +4874,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122373372</v>
+        <v>122373371</v>
       </c>
       <c r="B41" t="n">
         <v>57374</v>
@@ -4903,10 +4914,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480193</v>
+        <v>480198</v>
       </c>
       <c r="R41" t="n">
-        <v>7056693</v>
+        <v>7056685</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4970,7 +4981,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122373369</v>
+        <v>122373362</v>
       </c>
       <c r="B42" t="n">
         <v>57374</v>
@@ -5010,10 +5021,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479913</v>
+        <v>479917</v>
       </c>
       <c r="R42" t="n">
-        <v>7056490</v>
+        <v>7056160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5077,7 +5088,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122373371</v>
+        <v>122373346</v>
       </c>
       <c r="B43" t="n">
         <v>57374</v>
@@ -5117,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480198</v>
+        <v>480235</v>
       </c>
       <c r="R43" t="n">
-        <v>7056685</v>
+        <v>7056905</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5184,7 +5195,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122373380</v>
+        <v>122373345</v>
       </c>
       <c r="B44" t="n">
         <v>57374</v>
@@ -5224,10 +5235,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480203</v>
+        <v>480279</v>
       </c>
       <c r="R44" t="n">
-        <v>7056860</v>
+        <v>7056943</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5264,7 +5275,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5291,7 +5302,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122373377</v>
+        <v>122373349</v>
       </c>
       <c r="B45" t="n">
         <v>57374</v>
@@ -5331,10 +5342,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480176</v>
+        <v>480109</v>
       </c>
       <c r="R45" t="n">
-        <v>7056807</v>
+        <v>7056820</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5398,7 +5409,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122373360</v>
+        <v>122373355</v>
       </c>
       <c r="B46" t="n">
         <v>57374</v>
@@ -5438,10 +5449,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479860</v>
+        <v>479798</v>
       </c>
       <c r="R46" t="n">
-        <v>7056204</v>
+        <v>7056352</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,7 +5516,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122373359</v>
+        <v>122373367</v>
       </c>
       <c r="B47" t="n">
         <v>57374</v>
@@ -5545,10 +5556,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479854</v>
+        <v>479911</v>
       </c>
       <c r="R47" t="n">
-        <v>7056208</v>
+        <v>7056478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5585,7 +5596,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5612,7 +5623,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122373379</v>
+        <v>122373357</v>
       </c>
       <c r="B48" t="n">
         <v>57374</v>
@@ -5652,10 +5663,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480196</v>
+        <v>479865</v>
       </c>
       <c r="R48" t="n">
-        <v>7056852</v>
+        <v>7056258</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5692,7 +5703,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5719,10 +5730,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122373392</v>
+        <v>122373348</v>
       </c>
       <c r="B49" t="n">
-        <v>56584</v>
+        <v>57374</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5731,54 +5742,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480100</v>
+        <v>480205</v>
       </c>
       <c r="R49" t="n">
-        <v>7056572</v>
+        <v>7056888</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5811,6 +5806,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5837,7 +5837,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122373346</v>
+        <v>122373360</v>
       </c>
       <c r="B50" t="n">
         <v>57374</v>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480235</v>
+        <v>479860</v>
       </c>
       <c r="R50" t="n">
-        <v>7056905</v>
+        <v>7056204</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6054,7 +6054,7 @@
         <v>126697287</v>
       </c>
       <c r="B52" t="n">
-        <v>91832</v>
+        <v>91906</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>126695006</v>
       </c>
       <c r="B53" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126691912</v>
+        <v>126694229</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6266,34 +6266,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480491</v>
+        <v>480153</v>
       </c>
       <c r="R54" t="n">
-        <v>7057101</v>
+        <v>7056676</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6334,6 +6337,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6357,10 +6361,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126694229</v>
+        <v>126691912</v>
       </c>
       <c r="B55" t="n">
-        <v>91245</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6368,37 +6372,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480153</v>
+        <v>480491</v>
       </c>
       <c r="R55" t="n">
-        <v>7056676</v>
+        <v>7057101</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6439,7 +6440,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>126692587</v>
       </c>
       <c r="B56" t="n">
-        <v>77944</v>
+        <v>78004</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>126695450</v>
       </c>
       <c r="B57" t="n">
-        <v>88654</v>
+        <v>88722</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126694287</v>
+        <v>126693101</v>
       </c>
       <c r="B58" t="n">
-        <v>91245</v>
+        <v>91337</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,21 +6678,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480120</v>
+        <v>480162</v>
       </c>
       <c r="R58" t="n">
-        <v>7056666</v>
+        <v>7056779</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6769,10 +6769,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126693101</v>
+        <v>126691813</v>
       </c>
       <c r="B59" t="n">
-        <v>91263</v>
+        <v>80114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6780,21 +6780,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6804,10 +6804,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480162</v>
+        <v>480491</v>
       </c>
       <c r="R59" t="n">
-        <v>7056779</v>
+        <v>7057101</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6850,11 +6850,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6871,10 +6866,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126691813</v>
+        <v>126694287</v>
       </c>
       <c r="B60" t="n">
-        <v>80083</v>
+        <v>91319</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6882,21 +6877,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6906,10 +6901,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480491</v>
+        <v>480120</v>
       </c>
       <c r="R60" t="n">
-        <v>7057101</v>
+        <v>7056666</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6952,6 +6947,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6971,7 +6971,7 @@
         <v>126693738</v>
       </c>
       <c r="B61" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>126693837</v>
       </c>
       <c r="B62" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>126697900</v>
       </c>
       <c r="B63" t="n">
-        <v>91947</v>
+        <v>92021</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>126697199</v>
       </c>
       <c r="B64" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>126698441</v>
       </c>
       <c r="B65" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6054,7 +6054,7 @@
         <v>126697287</v>
       </c>
       <c r="B52" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>126695006</v>
       </c>
       <c r="B53" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126694229</v>
+        <v>126691912</v>
       </c>
       <c r="B54" t="n">
-        <v>91319</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6266,37 +6266,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480153</v>
+        <v>480491</v>
       </c>
       <c r="R54" t="n">
-        <v>7056676</v>
+        <v>7057101</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6337,7 +6334,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6361,10 +6357,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126691912</v>
+        <v>126694229</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>91325</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6372,34 +6368,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480491</v>
+        <v>480153</v>
       </c>
       <c r="R55" t="n">
-        <v>7057101</v>
+        <v>7056676</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6440,6 +6439,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>126692587</v>
       </c>
       <c r="B56" t="n">
-        <v>78004</v>
+        <v>78007</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>126695450</v>
       </c>
       <c r="B57" t="n">
-        <v>88722</v>
+        <v>88728</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126693101</v>
+        <v>126694287</v>
       </c>
       <c r="B58" t="n">
-        <v>91337</v>
+        <v>91325</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,21 +6678,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480162</v>
+        <v>480120</v>
       </c>
       <c r="R58" t="n">
-        <v>7056779</v>
+        <v>7056666</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6769,10 +6769,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126691813</v>
+        <v>126693101</v>
       </c>
       <c r="B59" t="n">
-        <v>80114</v>
+        <v>91343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6780,21 +6780,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6804,10 +6804,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480491</v>
+        <v>480162</v>
       </c>
       <c r="R59" t="n">
-        <v>7057101</v>
+        <v>7056779</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6850,6 +6850,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6866,10 +6871,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126694287</v>
+        <v>126691813</v>
       </c>
       <c r="B60" t="n">
-        <v>91319</v>
+        <v>80117</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6877,21 +6882,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6901,10 +6906,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480120</v>
+        <v>480491</v>
       </c>
       <c r="R60" t="n">
-        <v>7056666</v>
+        <v>7057101</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6947,11 +6952,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6971,7 +6971,7 @@
         <v>126693738</v>
       </c>
       <c r="B61" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>126693837</v>
       </c>
       <c r="B62" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>126697900</v>
       </c>
       <c r="B63" t="n">
-        <v>92021</v>
+        <v>92027</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>126697199</v>
       </c>
       <c r="B64" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>126698441</v>
       </c>
       <c r="B65" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6667,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126694287</v>
+        <v>126693101</v>
       </c>
       <c r="B58" t="n">
-        <v>91325</v>
+        <v>91343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,21 +6678,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480120</v>
+        <v>480162</v>
       </c>
       <c r="R58" t="n">
-        <v>7056666</v>
+        <v>7056779</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6769,10 +6769,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126693101</v>
+        <v>126691813</v>
       </c>
       <c r="B59" t="n">
-        <v>91343</v>
+        <v>80117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6780,21 +6780,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6804,10 +6804,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480162</v>
+        <v>480491</v>
       </c>
       <c r="R59" t="n">
-        <v>7056779</v>
+        <v>7057101</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6850,11 +6850,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6871,10 +6866,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126691813</v>
+        <v>126694287</v>
       </c>
       <c r="B60" t="n">
-        <v>80117</v>
+        <v>91325</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6882,21 +6877,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6906,10 +6901,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480491</v>
+        <v>480120</v>
       </c>
       <c r="R60" t="n">
-        <v>7057101</v>
+        <v>7056666</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6952,6 +6947,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6054,7 +6054,7 @@
         <v>126697287</v>
       </c>
       <c r="B52" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126691912</v>
+        <v>126694229</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6266,34 +6266,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480491</v>
+        <v>480153</v>
       </c>
       <c r="R54" t="n">
-        <v>7057101</v>
+        <v>7056676</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6334,6 +6337,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6357,10 +6361,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126694229</v>
+        <v>126691912</v>
       </c>
       <c r="B55" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6368,37 +6372,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480153</v>
+        <v>480491</v>
       </c>
       <c r="R55" t="n">
-        <v>7056676</v>
+        <v>7057101</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6439,7 +6440,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>126695450</v>
       </c>
       <c r="B57" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126693101</v>
+        <v>126694287</v>
       </c>
       <c r="B58" t="n">
-        <v>91343</v>
+        <v>91326</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,21 +6678,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480162</v>
+        <v>480120</v>
       </c>
       <c r="R58" t="n">
-        <v>7056779</v>
+        <v>7056666</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6769,10 +6769,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126691813</v>
+        <v>126693101</v>
       </c>
       <c r="B59" t="n">
-        <v>80117</v>
+        <v>91344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6780,21 +6780,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6804,10 +6804,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480491</v>
+        <v>480162</v>
       </c>
       <c r="R59" t="n">
-        <v>7057101</v>
+        <v>7056779</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6850,6 +6850,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6866,10 +6871,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126694287</v>
+        <v>126691813</v>
       </c>
       <c r="B60" t="n">
-        <v>91325</v>
+        <v>80117</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6877,21 +6882,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6901,10 +6906,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480120</v>
+        <v>480491</v>
       </c>
       <c r="R60" t="n">
-        <v>7056666</v>
+        <v>7057101</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6947,11 +6952,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6971,7 +6971,7 @@
         <v>126693738</v>
       </c>
       <c r="B61" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>126697900</v>
       </c>
       <c r="B63" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>126697199</v>
       </c>
       <c r="B64" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6667,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126694287</v>
+        <v>126691813</v>
       </c>
       <c r="B58" t="n">
-        <v>91326</v>
+        <v>80117</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,21 +6678,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480120</v>
+        <v>480491</v>
       </c>
       <c r="R58" t="n">
-        <v>7056666</v>
+        <v>7057101</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6748,11 +6748,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -6871,10 +6866,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126691813</v>
+        <v>126694287</v>
       </c>
       <c r="B60" t="n">
-        <v>80117</v>
+        <v>91326</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6882,21 +6877,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6906,10 +6901,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480491</v>
+        <v>480120</v>
       </c>
       <c r="R60" t="n">
-        <v>7057101</v>
+        <v>7056666</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6952,6 +6947,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6054,7 +6054,7 @@
         <v>126697287</v>
       </c>
       <c r="B52" t="n">
-        <v>91913</v>
+        <v>91906</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>126695006</v>
       </c>
       <c r="B53" t="n">
-        <v>82855</v>
+        <v>82852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>126694229</v>
       </c>
       <c r="B54" t="n">
-        <v>91326</v>
+        <v>91319</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>126691912</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>126692587</v>
       </c>
       <c r="B56" t="n">
-        <v>78007</v>
+        <v>78004</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>126695450</v>
       </c>
       <c r="B57" t="n">
-        <v>88729</v>
+        <v>88722</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126691813</v>
+        <v>126693101</v>
       </c>
       <c r="B58" t="n">
-        <v>80117</v>
+        <v>91337</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,21 +6678,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480491</v>
+        <v>480162</v>
       </c>
       <c r="R58" t="n">
-        <v>7057101</v>
+        <v>7056779</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6748,6 +6748,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -6764,10 +6769,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126693101</v>
+        <v>126691813</v>
       </c>
       <c r="B59" t="n">
-        <v>91344</v>
+        <v>80114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6775,21 +6780,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6799,10 +6804,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480162</v>
+        <v>480491</v>
       </c>
       <c r="R59" t="n">
-        <v>7056779</v>
+        <v>7057101</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6845,11 +6850,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6869,7 +6869,7 @@
         <v>126694287</v>
       </c>
       <c r="B60" t="n">
-        <v>91326</v>
+        <v>91319</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>126693738</v>
       </c>
       <c r="B61" t="n">
-        <v>91344</v>
+        <v>91337</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>126693837</v>
       </c>
       <c r="B62" t="n">
-        <v>75138</v>
+        <v>75135</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>126697900</v>
       </c>
       <c r="B63" t="n">
-        <v>92028</v>
+        <v>92021</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>126697199</v>
       </c>
       <c r="B64" t="n">
-        <v>91344</v>
+        <v>91337</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>126698441</v>
       </c>
       <c r="B65" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6054,7 +6054,7 @@
         <v>126697287</v>
       </c>
       <c r="B52" t="n">
-        <v>91913</v>
+        <v>92434</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6054,7 +6054,7 @@
         <v>126697287</v>
       </c>
       <c r="B52" t="n">
-        <v>92434</v>
+        <v>92440</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6054,7 +6054,7 @@
         <v>126697287</v>
       </c>
       <c r="B52" t="n">
-        <v>92440</v>
+        <v>92441</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6054,7 +6054,7 @@
         <v>126697287</v>
       </c>
       <c r="B52" t="n">
-        <v>92441</v>
+        <v>92442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -6054,7 +6054,7 @@
         <v>126697287</v>
       </c>
       <c r="B52" t="n">
-        <v>92442</v>
+        <v>92445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122373356</v>
+        <v>126697900</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tornäs sv, Jmt</t>
+          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479919</v>
+        <v>479884</v>
       </c>
       <c r="R2" t="n">
-        <v>7056272</v>
+        <v>7056348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,66 +756,66 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122373377</v>
+        <v>126692587</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tornäs sv, Jmt</t>
+          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480176</v>
+        <v>480284</v>
       </c>
       <c r="R3" t="n">
-        <v>7056807</v>
+        <v>7056984</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,31 +858,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122373380</v>
+        <v>126695450</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tornäs sv, Jmt</t>
+          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480203</v>
+        <v>479944</v>
       </c>
       <c r="R4" t="n">
-        <v>7056860</v>
+        <v>7056550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,17 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,66 +960,66 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122373366</v>
+        <v>126697287</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tornäs sv, Jmt</t>
+          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479875</v>
+        <v>479950</v>
       </c>
       <c r="R5" t="n">
-        <v>7056356</v>
+        <v>7056266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,17 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,31 +1062,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122373389</v>
+        <v>126694229</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tornäs sv, Jmt</t>
+          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480418</v>
+        <v>480153</v>
       </c>
       <c r="R6" t="n">
-        <v>7056980</v>
+        <v>7056676</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,17 +1151,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,33 +1165,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122373361</v>
+        <v>126694287</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1200,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tornäs sv, Jmt</t>
+          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479902</v>
+        <v>480120</v>
       </c>
       <c r="R7" t="n">
-        <v>7056188</v>
+        <v>7056666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,17 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,31 +1270,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122373398</v>
+        <v>126695006</v>
       </c>
       <c r="B8" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,34 +1302,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tornäs sv, Jmt</t>
+          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480268</v>
+        <v>479988</v>
       </c>
       <c r="R8" t="n">
-        <v>7056775</v>
+        <v>7056573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,12 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,53 +1372,53 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122373355</v>
+        <v>122373397</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479798</v>
+        <v>480312</v>
       </c>
       <c r="R9" t="n">
-        <v>7056352</v>
+        <v>7056795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1464,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,37 +1490,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122373382</v>
+        <v>122373398</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480323</v>
+        <v>480268</v>
       </c>
       <c r="R10" t="n">
-        <v>7056911</v>
+        <v>7056775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,15 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122373357</v>
+        <v>126693837</v>
       </c>
       <c r="B11" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,34 +1598,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tornäs sv, Jmt</t>
+          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479865</v>
+        <v>480178</v>
       </c>
       <c r="R11" t="n">
-        <v>7056258</v>
+        <v>7056699</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,17 +1652,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,31 +1668,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Stamtät och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122373374</v>
+        <v>122373342</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480232</v>
+        <v>480287</v>
       </c>
       <c r="R12" t="n">
-        <v>7056719</v>
+        <v>7056982</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,15 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122373348</v>
+        <v>122373344</v>
       </c>
       <c r="B13" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480205</v>
+        <v>480283</v>
       </c>
       <c r="R13" t="n">
-        <v>7056888</v>
+        <v>7056981</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,15 +1893,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122373344</v>
+        <v>122373345</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1928,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480283</v>
+        <v>480279</v>
       </c>
       <c r="R14" t="n">
-        <v>7056981</v>
+        <v>7056943</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,15 +1995,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122373369</v>
+        <v>122373346</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479913</v>
+        <v>480235</v>
       </c>
       <c r="R15" t="n">
-        <v>7056490</v>
+        <v>7056905</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,15 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122373373</v>
+        <v>122373347</v>
       </c>
       <c r="B16" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480214</v>
+        <v>480230</v>
       </c>
       <c r="R16" t="n">
-        <v>7056710</v>
+        <v>7056904</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,15 +2199,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122373368</v>
+        <v>122373348</v>
       </c>
       <c r="B17" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479912</v>
+        <v>480205</v>
       </c>
       <c r="R17" t="n">
-        <v>7056484</v>
+        <v>7056888</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,15 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122373353</v>
+        <v>122373349</v>
       </c>
       <c r="B18" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479911</v>
+        <v>480109</v>
       </c>
       <c r="R18" t="n">
-        <v>7056543</v>
+        <v>7056820</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2376,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,15 +2403,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122373358</v>
+        <v>122373350</v>
       </c>
       <c r="B19" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,10 +2438,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479856</v>
+        <v>480089</v>
       </c>
       <c r="R19" t="n">
-        <v>7056220</v>
+        <v>7056809</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2478,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,32 +2505,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122373396</v>
+        <v>122373351</v>
       </c>
       <c r="B20" t="n">
-        <v>57495</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2629,25 +2533,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480182</v>
+        <v>480019</v>
       </c>
       <c r="R20" t="n">
-        <v>7056798</v>
+        <v>7056686</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,6 +2576,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,15 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122373363</v>
+        <v>122373352</v>
       </c>
       <c r="B21" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479932</v>
+        <v>479988</v>
       </c>
       <c r="R21" t="n">
-        <v>7056162</v>
+        <v>7056637</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2786,7 +2682,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,15 +2709,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122373365</v>
+        <v>122373353</v>
       </c>
       <c r="B22" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2853,10 +2744,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479882</v>
+        <v>479911</v>
       </c>
       <c r="R22" t="n">
-        <v>7056347</v>
+        <v>7056543</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,7 +2784,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,15 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122373397</v>
+        <v>122373354</v>
       </c>
       <c r="B23" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2960,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480312</v>
+        <v>479919</v>
       </c>
       <c r="R23" t="n">
-        <v>7056795</v>
+        <v>7056527</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,6 +2882,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,15 +2913,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122373347</v>
+        <v>122373355</v>
       </c>
       <c r="B24" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,10 +2948,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480230</v>
+        <v>479798</v>
       </c>
       <c r="R24" t="n">
-        <v>7056904</v>
+        <v>7056352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,7 +2988,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,15 +3015,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122373378</v>
+        <v>122373356</v>
       </c>
       <c r="B25" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480182</v>
+        <v>479919</v>
       </c>
       <c r="R25" t="n">
-        <v>7056855</v>
+        <v>7056272</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,7 +3090,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,15 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122373345</v>
+        <v>122373357</v>
       </c>
       <c r="B26" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3276,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480279</v>
+        <v>479865</v>
       </c>
       <c r="R26" t="n">
-        <v>7056943</v>
+        <v>7056258</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3316,7 +3192,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,15 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122373360</v>
+        <v>122373358</v>
       </c>
       <c r="B27" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3383,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479860</v>
+        <v>479856</v>
       </c>
       <c r="R27" t="n">
-        <v>7056204</v>
+        <v>7056220</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3450,66 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122373392</v>
+        <v>122373359</v>
       </c>
       <c r="B28" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480100</v>
+        <v>479854</v>
       </c>
       <c r="R28" t="n">
-        <v>7056572</v>
+        <v>7056208</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,6 +3392,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3568,15 +3423,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122373384</v>
+        <v>122373360</v>
       </c>
       <c r="B29" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3608,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480354</v>
+        <v>479860</v>
       </c>
       <c r="R29" t="n">
-        <v>7056915</v>
+        <v>7056204</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,15 +3525,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122373346</v>
+        <v>122373361</v>
       </c>
       <c r="B30" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,10 +3560,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480235</v>
+        <v>479902</v>
       </c>
       <c r="R30" t="n">
-        <v>7056905</v>
+        <v>7056188</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3782,15 +3627,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122373342</v>
+        <v>122373362</v>
       </c>
       <c r="B31" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3822,10 +3662,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480287</v>
+        <v>479917</v>
       </c>
       <c r="R31" t="n">
-        <v>7056982</v>
+        <v>7056160</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3889,15 +3729,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122373350</v>
+        <v>122373363</v>
       </c>
       <c r="B32" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3929,10 +3764,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480089</v>
+        <v>479932</v>
       </c>
       <c r="R32" t="n">
-        <v>7056809</v>
+        <v>7056162</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,15 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122373386</v>
+        <v>122373365</v>
       </c>
       <c r="B33" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4036,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480360</v>
+        <v>479882</v>
       </c>
       <c r="R33" t="n">
-        <v>7056924</v>
+        <v>7056347</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,7 +3906,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4103,15 +3933,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122373349</v>
+        <v>122373366</v>
       </c>
       <c r="B34" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4143,10 +3968,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480109</v>
+        <v>479875</v>
       </c>
       <c r="R34" t="n">
-        <v>7056820</v>
+        <v>7056356</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4183,7 +4008,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4210,15 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122373393</v>
+        <v>122373367</v>
       </c>
       <c r="B35" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4226,46 +4046,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480298</v>
+        <v>479911</v>
       </c>
       <c r="R35" t="n">
-        <v>7056795</v>
+        <v>7056478</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4298,6 +4106,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,15 +4137,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122373351</v>
+        <v>122373368</v>
       </c>
       <c r="B36" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4364,10 +4172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480019</v>
+        <v>479912</v>
       </c>
       <c r="R36" t="n">
-        <v>7056686</v>
+        <v>7056484</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4404,7 +4212,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4431,15 +4239,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122373367</v>
+        <v>122373369</v>
       </c>
       <c r="B37" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,10 +4274,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479911</v>
+        <v>479913</v>
       </c>
       <c r="R37" t="n">
-        <v>7056478</v>
+        <v>7056490</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4538,15 +4341,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122373354</v>
+        <v>122373370</v>
       </c>
       <c r="B38" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4578,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479919</v>
+        <v>480000</v>
       </c>
       <c r="R38" t="n">
-        <v>7056527</v>
+        <v>7056521</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4645,15 +4443,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122373385</v>
+        <v>122373371</v>
       </c>
       <c r="B39" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,10 +4478,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480361</v>
+        <v>480198</v>
       </c>
       <c r="R39" t="n">
-        <v>7056919</v>
+        <v>7056685</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4725,7 +4518,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4752,15 +4545,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122373352</v>
+        <v>122373372</v>
       </c>
       <c r="B40" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4792,10 +4580,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479988</v>
+        <v>480193</v>
       </c>
       <c r="R40" t="n">
-        <v>7056637</v>
+        <v>7056693</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4859,15 +4647,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122373362</v>
+        <v>122373373</v>
       </c>
       <c r="B41" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4899,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479917</v>
+        <v>480214</v>
       </c>
       <c r="R41" t="n">
-        <v>7056160</v>
+        <v>7056710</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4939,7 +4722,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4966,15 +4749,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122373381</v>
+        <v>122373374</v>
       </c>
       <c r="B42" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5006,10 +4784,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480295</v>
+        <v>480232</v>
       </c>
       <c r="R42" t="n">
-        <v>7056917</v>
+        <v>7056719</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5046,7 +4824,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5073,15 +4851,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122373376</v>
+        <v>122373375</v>
       </c>
       <c r="B43" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5106,37 +4879,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480199</v>
+        <v>480254</v>
       </c>
       <c r="R43" t="n">
-        <v>7056785</v>
+        <v>7056771</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5169,6 +4922,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5195,15 +4953,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122373383</v>
+        <v>122373376</v>
       </c>
       <c r="B44" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,17 +4981,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480360</v>
+        <v>480199</v>
       </c>
       <c r="R44" t="n">
-        <v>7056891</v>
+        <v>7056785</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5271,11 +5044,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5302,15 +5070,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122373388</v>
+        <v>122373377</v>
       </c>
       <c r="B45" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,10 +5105,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480408</v>
+        <v>480176</v>
       </c>
       <c r="R45" t="n">
-        <v>7056973</v>
+        <v>7056807</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5409,15 +5172,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122373370</v>
+        <v>122373378</v>
       </c>
       <c r="B46" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5449,10 +5207,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480000</v>
+        <v>480182</v>
       </c>
       <c r="R46" t="n">
-        <v>7056521</v>
+        <v>7056855</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,15 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122373371</v>
+        <v>122373379</v>
       </c>
       <c r="B47" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5556,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480198</v>
+        <v>480196</v>
       </c>
       <c r="R47" t="n">
-        <v>7056685</v>
+        <v>7056852</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5623,15 +5376,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122373372</v>
+        <v>122373380</v>
       </c>
       <c r="B48" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5663,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480193</v>
+        <v>480203</v>
       </c>
       <c r="R48" t="n">
-        <v>7056693</v>
+        <v>7056860</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5703,7 +5451,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5730,15 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122373375</v>
+        <v>122373381</v>
       </c>
       <c r="B49" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5770,10 +5513,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480254</v>
+        <v>480295</v>
       </c>
       <c r="R49" t="n">
-        <v>7056771</v>
+        <v>7056917</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5837,15 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122373359</v>
+        <v>122373382</v>
       </c>
       <c r="B50" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5877,10 +5615,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479854</v>
+        <v>480323</v>
       </c>
       <c r="R50" t="n">
-        <v>7056208</v>
+        <v>7056911</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5917,7 +5655,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5944,15 +5682,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122373379</v>
+        <v>122373383</v>
       </c>
       <c r="B51" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,10 +5717,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480196</v>
+        <v>480360</v>
       </c>
       <c r="R51" t="n">
-        <v>7056852</v>
+        <v>7056891</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6024,7 +5757,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6051,45 +5784,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126697287</v>
+        <v>122373384</v>
       </c>
       <c r="B52" t="n">
-        <v>92461</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1179</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
+          <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479950</v>
+        <v>480354</v>
       </c>
       <c r="R52" t="n">
-        <v>7056266</v>
+        <v>7056915</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6116,12 +5849,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,31 +5870,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126695006</v>
+        <v>122373385</v>
       </c>
       <c r="B53" t="n">
-        <v>82855</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,34 +5897,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
+          <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479988</v>
+        <v>480361</v>
       </c>
       <c r="R53" t="n">
-        <v>7056573</v>
+        <v>7056919</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6218,12 +5951,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6234,31 +5972,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126694229</v>
+        <v>122373386</v>
       </c>
       <c r="B54" t="n">
-        <v>91326</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6266,37 +5999,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
+          <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480153</v>
+        <v>480360</v>
       </c>
       <c r="R54" t="n">
-        <v>7056676</v>
+        <v>7056924</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6323,12 +6053,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6337,34 +6072,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126691912</v>
+        <v>122373388</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6372,34 +6101,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
+          <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480491</v>
+        <v>480408</v>
       </c>
       <c r="R55" t="n">
-        <v>7057101</v>
+        <v>7056973</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6426,12 +6155,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6442,31 +6176,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126692587</v>
+        <v>122373389</v>
       </c>
       <c r="B56" t="n">
-        <v>78007</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6474,34 +6203,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
+          <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480284</v>
+        <v>480418</v>
       </c>
       <c r="R56" t="n">
-        <v>7056984</v>
+        <v>7056980</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6528,12 +6257,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6544,66 +6278,77 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126695450</v>
+        <v>122373392</v>
       </c>
       <c r="B57" t="n">
-        <v>88729</v>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
+          <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479944</v>
+        <v>480100</v>
       </c>
       <c r="R57" t="n">
-        <v>7056550</v>
+        <v>7056572</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,12 +6375,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6646,31 +6391,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126691813</v>
+        <v>122373393</v>
       </c>
       <c r="B58" t="n">
-        <v>80117</v>
+        <v>58114</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,34 +6418,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
+          <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480491</v>
+        <v>480298</v>
       </c>
       <c r="R58" t="n">
-        <v>7057101</v>
+        <v>7056795</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6732,12 +6484,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6752,22 +6504,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126693101</v>
+        <v>122373396</v>
       </c>
       <c r="B59" t="n">
-        <v>91344</v>
+        <v>58057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6775,34 +6527,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
+          <t>Tornäs sv, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480162</v>
+        <v>480182</v>
       </c>
       <c r="R59" t="n">
-        <v>7056779</v>
+        <v>7056798</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6829,12 +6589,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6845,31 +6605,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126694287</v>
+        <v>126698441</v>
       </c>
       <c r="B60" t="n">
-        <v>91326</v>
+        <v>79085</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6877,34 +6632,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gunnelmyren, Gunnelmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480120</v>
+        <v>480460</v>
       </c>
       <c r="R60" t="n">
-        <v>7056666</v>
+        <v>7057060</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6945,12 +6703,13 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Stamtät och lövrik grannaturskog</t>
+          <t>Barrblandskog på ås, tidigare brandpåverkat område</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -6968,32 +6727,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126693738</v>
+        <v>126691912</v>
       </c>
       <c r="B61" t="n">
-        <v>91344</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7003,10 +6762,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480219</v>
+        <v>480491</v>
       </c>
       <c r="R61" t="n">
-        <v>7056733</v>
+        <v>7057101</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7070,10 +6829,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126693837</v>
+        <v>126691813</v>
       </c>
       <c r="B62" t="n">
-        <v>75138</v>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7081,21 +6840,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7105,10 +6864,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480178</v>
+        <v>480491</v>
       </c>
       <c r="R62" t="n">
-        <v>7056699</v>
+        <v>7057101</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7152,11 +6911,6 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7169,316 +6923,6 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>126697900</v>
-      </c>
-      <c r="B63" t="n">
-        <v>92028</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>67</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Sprickporing</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Diplomitoporus crustulinus</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>479884</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7056348</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>126697199</v>
-      </c>
-      <c r="B64" t="n">
-        <v>91344</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>479954</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7056263</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Stamtät och lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>126698441</v>
-      </c>
-      <c r="B65" t="n">
-        <v>78773</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Gunnelmyren, Gunnelmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>480460</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7057060</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Barrblandskog på ås, tidigare brandpåverkat område</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 394-2025 artfynd.xlsx
+++ b/artfynd/A 394-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697900</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126692587</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126695450</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697287</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126694229</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126694287</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126695006</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373397</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373398</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126691912</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126693837</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126691813</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373342</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2089,6 +2159,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373344</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373345</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373346</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2395,6 +2480,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373347</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2497,6 +2587,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373348</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373349</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2701,6 +2801,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373350</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373351</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2905,6 +3015,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373352</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3007,6 +3122,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373353</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3109,6 +3229,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373354</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3211,6 +3336,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373355</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3313,6 +3443,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373356</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3415,6 +3550,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373357</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3517,6 +3657,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373358</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3619,6 +3764,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373359</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3721,6 +3871,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373360</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3823,6 +3978,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373361</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3925,6 +4085,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373362</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4027,6 +4192,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373363</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4129,6 +4299,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373365</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4231,6 +4406,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373366</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4333,6 +4513,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373367</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4435,6 +4620,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373368</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4537,6 +4727,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373369</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4639,6 +4834,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373370</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4741,6 +4941,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373371</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4843,6 +5048,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373372</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4945,6 +5155,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373373</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5047,6 +5262,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373374</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5149,6 +5369,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373375</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5266,6 +5491,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373376</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5368,6 +5598,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373377</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5470,6 +5705,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373378</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5572,6 +5812,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373379</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5674,6 +5919,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373380</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5776,6 +6026,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373381</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5878,6 +6133,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373382</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5980,6 +6240,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373383</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6082,6 +6347,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373384</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6184,6 +6454,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373385</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6286,6 +6561,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373386</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6388,6 +6668,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373388</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6490,6 +6775,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373389</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6603,6 +6893,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373392</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6712,6 +7007,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373393</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6817,6 +7117,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122373396</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6923,8 +7228,76 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126698441</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>